--- a/reports/pdf_rolling5_20260707.xlsx
+++ b/reports/pdf_rolling5_20260707.xlsx
@@ -575,7 +575,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,385억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 13종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,102억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 13종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -671,10 +671,10 @@
         <v>52</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>571605840</v>
+        <v>574844400</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.106</v>
+        <v>0.113</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -690,10 +690,10 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1114173900</v>
+        <v>-1120486500</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-0.207</v>
+        <v>-0.22</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>45</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2058696000</v>
+        <v>2070360000</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.382</v>
+        <v>0.406</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         <v>-49</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2786546700</v>
+        <v>-2802334500</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-0.518</v>
+        <v>-0.549</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -751,10 +751,10 @@
         <v>33</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1362933000</v>
+        <v>1370655000</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.253</v>
+        <v>0.269</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         <v>-38</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-3448739400</v>
+        <v>-3468279000</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.64</v>
+        <v>-0.68</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         <v>33</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3120767100</v>
+        <v>3138448500</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.58</v>
+        <v>0.615</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         <v>-36</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-492562080</v>
+        <v>-495352800</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.091</v>
+        <v>-0.097</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>503596860</v>
+        <v>506450100</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-5399311500</v>
+        <v>-5429902500</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>-1.003</v>
+        <v>-1.064</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -871,10 +871,10 @@
         <v>27</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1075096800</v>
+        <v>1081188000</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.2</v>
+        <v>0.212</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
         <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-3732339600</v>
+        <v>-3753486000</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.736</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1977682500</v>
+        <v>1988887500</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.367</v>
+        <v>0.39</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         <v>-24</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2173068000</v>
+        <v>-2185380000</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-0.404</v>
+        <v>-0.428</v>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>534689100</v>
+        <v>537718500</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.099</v>
+        <v>0.105</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         <v>-19</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1559377500</v>
+        <v>-1568212500</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>-0.29</v>
+        <v>-0.307</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1347048000</v>
+        <v>1354680000</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2900601000</v>
+        <v>-2917035000</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>-0.539</v>
+        <v>-0.572</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1054764000</v>
+        <v>1060740000</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.196</v>
+        <v>0.208</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
         <v>-3</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-776776500</v>
+        <v>-781177500</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>-0.144</v>
+        <v>-0.153</v>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>449863200</v>
+        <v>452412000</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>401890500</v>
+        <v>404167500</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.075</v>
+        <v>0.079</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1402116000</v>
+        <v>1410060000</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.26</v>
+        <v>0.276</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,769억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,517억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1238,10 +1238,10 @@
         <v>68</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>456688000</v>
+        <v>458252000</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.096</v>
+        <v>0.101</v>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         <v>-20</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1576800000</v>
+        <v>-1582200000</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>-0.331</v>
+        <v>-0.35</v>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1482192000</v>
+        <v>1487268000</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.311</v>
+        <v>0.329</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,420억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,251억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1393,10 +1393,10 @@
         <v>21</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2185785000</v>
+        <v>2208465000</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.639</v>
+        <v>0.679</v>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         <v>-39</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2685161700</v>
+        <v>-2713023300</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>-0.785</v>
+        <v>-0.835</v>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,814억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,694억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1450,7 +1450,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 366억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 18종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 356억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 18종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1546,10 +1546,10 @@
         <v>91</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>23769200</v>
+        <v>24214190</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         <v>-268</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-145363200</v>
+        <v>-149656560</v>
       </c>
       <c r="J37" s="16" t="n">
-        <v>-0.397</v>
+        <v>-0.42</v>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         <v>80</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>63872000</v>
+        <v>61204800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.175</v>
+        <v>0.172</v>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
@@ -1605,10 +1605,10 @@
         <v>-111</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-221112000</v>
+        <v>-222999000</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>-0.604</v>
+        <v>-0.626</v>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
@@ -1626,10 +1626,10 @@
         <v>27</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>41709600</v>
+        <v>42375960</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.114</v>
+        <v>0.119</v>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
@@ -1638,21 +1638,21 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>다우데이타</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-63</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-182700000</v>
+        <v>-98463960</v>
       </c>
       <c r="J39" s="16" t="n">
-        <v>-0.499</v>
+        <v>-0.276</v>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>796→733</t>
+          <t>107→44</t>
         </is>
       </c>
     </row>
@@ -1666,10 +1666,10 @@
         <v>23</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>93104000</v>
+        <v>92508300</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.254</v>
+        <v>0.26</v>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
@@ -1678,21 +1678,21 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>다우데이타</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-63</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-94147200</v>
+        <v>-178485300</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>-0.257</v>
+        <v>-0.501</v>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>107→44</t>
+          <t>796→733</t>
         </is>
       </c>
     </row>
@@ -1706,10 +1706,10 @@
         <v>21</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>56868000</v>
+        <v>56223300</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.155</v>
+        <v>0.158</v>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-40992000</v>
+        <v>-55391000</v>
       </c>
       <c r="J41" s="16" t="n">
-        <v>-0.112</v>
+        <v>-0.155</v>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>210→196</t>
         </is>
       </c>
     </row>
@@ -1746,10 +1746,10 @@
         <v>19</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>77368000</v>
+        <v>73148100</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.211</v>
+        <v>0.205</v>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-58016000</v>
+        <v>-41442800</v>
       </c>
       <c r="J42" s="16" t="n">
-        <v>-0.159</v>
+        <v>-0.116</v>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>210→196</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -1786,10 +1786,10 @@
         <v>17</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>181016000</v>
+        <v>173553000</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.495</v>
+        <v>0.487</v>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         <v>-13</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-111800000</v>
+        <v>-113848800</v>
       </c>
       <c r="J43" s="16" t="n">
-        <v>-0.305</v>
+        <v>-0.32</v>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
@@ -1826,10 +1826,10 @@
         <v>12</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>55392000</v>
+        <v>54218400</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         <v>-13</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-36348000</v>
+        <v>-39442000</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>-0.099</v>
+        <v>-0.111</v>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         <v>11</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>19448000</v>
+        <v>19167500</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         <v>-9</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-60768000</v>
+        <v>-57195000</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>-0.166</v>
+        <v>-0.161</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         <v>10</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>141840000</v>
+        <v>131528000</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.388</v>
+        <v>0.369</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
         <v>-9</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-103608000</v>
+        <v>-93873600</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>-0.283</v>
+        <v>-0.264</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
         <v>10</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>62960000</v>
+        <v>63632000</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.172</v>
+        <v>0.179</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
         <v>-8</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-166400000</v>
+        <v>-178432000</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.455</v>
+        <v>-0.501</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>9</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>120240000</v>
+        <v>112692600</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.329</v>
+        <v>0.316</v>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         <v>-4</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-41312000</v>
+        <v>-38868000</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-0.113</v>
+        <v>-0.109</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         <v>8</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>116672000</v>
+        <v>112044800</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.319</v>
+        <v>0.315</v>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
         <v>6</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>40464000</v>
+        <v>40344000</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>42720000</v>
+        <v>42115200</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
         <v>5</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>21640000</v>
+        <v>20151500</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
         <v>4</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>103200000</v>
+        <v>103156000</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.282</v>
+        <v>0.29</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         <v>3</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>58800000</v>
+        <v>58794000</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.161</v>
+        <v>0.165</v>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 6종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억      오늘 2026-07-07  vs  5일전 2026-06-30      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -2271,10 +2271,10 @@
         <v>297</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>856132200</v>
+        <v>878273550</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>1.355</v>
+        <v>1.475</v>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
         <v>-685</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-891541200</v>
+        <v>-914598300</v>
       </c>
       <c r="J59" s="16" t="n">
-        <v>-1.411</v>
+        <v>-1.536</v>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         <v>77</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>152469240</v>
+        <v>156412410</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.241</v>
+        <v>0.263</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
         <v>-122</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-1910520000</v>
+        <v>-1959930000</v>
       </c>
       <c r="J60" s="16" t="n">
-        <v>-3.023</v>
+        <v>-3.291</v>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         <v>35</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>714154000</v>
+        <v>732623500</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
@@ -2370,10 +2370,10 @@
         <v>-36</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-533692800</v>
+        <v>-547495200</v>
       </c>
       <c r="J61" s="16" t="n">
-        <v>-0.844</v>
+        <v>-0.919</v>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         <v>16</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>785088000</v>
+        <v>805392000</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>1.242</v>
+        <v>1.352</v>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         <v>-13</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-499148000</v>
+        <v>-512057000</v>
       </c>
       <c r="J62" s="16" t="n">
-        <v>-0.79</v>
+        <v>-0.86</v>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         <v>14</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>509936000</v>
+        <v>523124000</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.878</v>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
         <v>4</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>41852800</v>
+        <v>42935200</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.066</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260707.xlsx
+++ b/reports/pdf_rolling5_20260707.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
-    <numFmt numFmtId="165" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -158,7 +157,7 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,7 +167,7 @@
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -627,7 +626,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -652,7 +651,7 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -673,8 +672,10 @@
       <c r="C6" s="11" t="n">
         <v>574844400</v>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>0.113</v>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>1.02%→1.27%</t>
+        </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -692,8 +693,10 @@
       <c r="I6" s="15" t="n">
         <v>-1120486500</v>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>-0.22</v>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.00%</t>
+        </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -713,8 +716,10 @@
       <c r="C7" s="11" t="n">
         <v>2070360000</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>0.406</v>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.41%</t>
+        </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -732,8 +737,10 @@
       <c r="I7" s="15" t="n">
         <v>-2802334500</v>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>-0.549</v>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.49%→0.00%</t>
+        </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -753,8 +760,10 @@
       <c r="C8" s="11" t="n">
         <v>1370655000</v>
       </c>
-      <c r="D8" s="12" t="n">
-        <v>0.269</v>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.40%→1.53%</t>
+        </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -772,8 +781,10 @@
       <c r="I8" s="15" t="n">
         <v>-3468279000</v>
       </c>
-      <c r="J8" s="16" t="n">
-        <v>-0.68</v>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.61%→0.00%</t>
+        </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -793,8 +804,10 @@
       <c r="C9" s="11" t="n">
         <v>3138448500</v>
       </c>
-      <c r="D9" s="12" t="n">
-        <v>0.615</v>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>2.02%→2.74%</t>
+        </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -812,8 +825,10 @@
       <c r="I9" s="15" t="n">
         <v>-495352800</v>
       </c>
-      <c r="J9" s="16" t="n">
-        <v>-0.097</v>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.49%</t>
+        </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -833,8 +848,10 @@
       <c r="C10" s="11" t="n">
         <v>506450100</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>0.099</v>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>0.32%→0.35%</t>
+        </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -852,8 +869,10 @@
       <c r="I10" s="15" t="n">
         <v>-5429902500</v>
       </c>
-      <c r="J10" s="16" t="n">
-        <v>-1.064</v>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.96%→0.00%</t>
+        </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -873,8 +892,10 @@
       <c r="C11" s="11" t="n">
         <v>1081188000</v>
       </c>
-      <c r="D11" s="12" t="n">
-        <v>0.212</v>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.22%</t>
+        </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -892,8 +913,10 @@
       <c r="I11" s="15" t="n">
         <v>-3753486000</v>
       </c>
-      <c r="J11" s="16" t="n">
-        <v>-0.736</v>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>1.63%→0.93%</t>
+        </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -913,8 +936,10 @@
       <c r="C12" s="11" t="n">
         <v>1988887500</v>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>0.39</v>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>0.75%→1.06%</t>
+        </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -932,8 +957,10 @@
       <c r="I12" s="15" t="n">
         <v>-2185380000</v>
       </c>
-      <c r="J12" s="16" t="n">
-        <v>-0.428</v>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>1.09%→0.46%</t>
+        </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -953,8 +980,10 @@
       <c r="C13" s="11" t="n">
         <v>537718500</v>
       </c>
-      <c r="D13" s="12" t="n">
-        <v>0.105</v>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>1.24%→1.58%</t>
+        </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -972,8 +1001,10 @@
       <c r="I13" s="15" t="n">
         <v>-1568212500</v>
       </c>
-      <c r="J13" s="16" t="n">
-        <v>-0.307</v>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>1.19%→0.94%</t>
+        </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -993,8 +1024,10 @@
       <c r="C14" s="11" t="n">
         <v>1354680000</v>
       </c>
-      <c r="D14" s="12" t="n">
-        <v>0.265</v>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>2.93%→3.42%</t>
+        </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1012,8 +1045,10 @@
       <c r="I14" s="15" t="n">
         <v>-2917035000</v>
       </c>
-      <c r="J14" s="16" t="n">
-        <v>-0.572</v>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.00%</t>
+        </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1033,8 +1068,10 @@
       <c r="C15" s="11" t="n">
         <v>1060740000</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <v>0.208</v>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>1.09%→1.35%</t>
+        </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -1052,8 +1089,10 @@
       <c r="I15" s="15" t="n">
         <v>-781177500</v>
       </c>
-      <c r="J15" s="16" t="n">
-        <v>-0.153</v>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>1.85%→2.14%</t>
+        </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
@@ -1073,8 +1112,10 @@
       <c r="C16" s="11" t="n">
         <v>452412000</v>
       </c>
-      <c r="D16" s="12" t="n">
-        <v>0.089</v>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>2.48%→2.72%</t>
+        </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -1099,8 +1140,10 @@
       <c r="C17" s="11" t="n">
         <v>404167500</v>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>0.079</v>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>0.94%→0.95%</t>
+        </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -1125,8 +1168,10 @@
       <c r="C18" s="11" t="n">
         <v>1410060000</v>
       </c>
-      <c r="D18" s="12" t="n">
-        <v>0.276</v>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>3.36%→3.67%</t>
+        </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -1194,7 +1239,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1219,7 +1264,7 @@
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -1240,8 +1285,10 @@
       <c r="C23" s="11" t="n">
         <v>458252000</v>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>0.101</v>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>1.21%→1.48%</t>
+        </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
@@ -1259,8 +1306,10 @@
       <c r="I23" s="15" t="n">
         <v>-1582200000</v>
       </c>
-      <c r="J23" s="16" t="n">
-        <v>-0.35</v>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>9.73%→8.70%</t>
+        </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
@@ -1280,8 +1329,10 @@
       <c r="C24" s="11" t="n">
         <v>1487268000</v>
       </c>
-      <c r="D24" s="12" t="n">
-        <v>0.329</v>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>4.84%→5.85%</t>
+        </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1349,7 +1400,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1374,7 +1425,7 @@
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -1395,8 +1446,10 @@
       <c r="C29" s="11" t="n">
         <v>2208465000</v>
       </c>
-      <c r="D29" s="12" t="n">
-        <v>0.679</v>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>0.70%→1.32%</t>
+        </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -1414,8 +1467,10 @@
       <c r="I29" s="15" t="n">
         <v>-2713023300</v>
       </c>
-      <c r="J29" s="16" t="n">
-        <v>-0.835</v>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>4.06%→3.28%</t>
+        </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -1502,7 +1557,7 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -1527,7 +1582,7 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -1548,8 +1603,10 @@
       <c r="C37" s="11" t="n">
         <v>24214190</v>
       </c>
-      <c r="D37" s="12" t="n">
-        <v>0.068</v>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>0.39%→0.46%</t>
+        </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
@@ -1567,8 +1624,10 @@
       <c r="I37" s="15" t="n">
         <v>-149656560</v>
       </c>
-      <c r="J37" s="16" t="n">
-        <v>-0.42</v>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>0.73%→0.30%</t>
+        </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
@@ -1588,8 +1647,10 @@
       <c r="C38" s="11" t="n">
         <v>61204800</v>
       </c>
-      <c r="D38" s="12" t="n">
-        <v>0.172</v>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>6.50%→6.67%</t>
+        </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
@@ -1607,8 +1668,10 @@
       <c r="I38" s="15" t="n">
         <v>-222999000</v>
       </c>
-      <c r="J38" s="16" t="n">
-        <v>-0.626</v>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>3.76%→3.11%</t>
+        </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
@@ -1628,8 +1691,10 @@
       <c r="C39" s="11" t="n">
         <v>42375960</v>
       </c>
-      <c r="D39" s="12" t="n">
-        <v>0.119</v>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>0.26%→0.39%</t>
+        </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
@@ -1638,21 +1703,23 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>다우데이타</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-63</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-98463960</v>
-      </c>
-      <c r="J39" s="16" t="n">
-        <v>-0.276</v>
+        <v>-178485300</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>6.52%→6.00%</t>
+        </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>107→44</t>
+          <t>796→733</t>
         </is>
       </c>
     </row>
@@ -1668,8 +1735,10 @@
       <c r="C40" s="11" t="n">
         <v>92508300</v>
       </c>
-      <c r="D40" s="12" t="n">
-        <v>0.26</v>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>1.56%→1.82%</t>
+        </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
@@ -1678,21 +1747,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>다우데이타</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-63</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-178485300</v>
-      </c>
-      <c r="J40" s="16" t="n">
-        <v>-0.501</v>
+        <v>-98463960</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>0.48%→0.20%</t>
+        </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>796→733</t>
+          <t>107→44</t>
         </is>
       </c>
     </row>
@@ -1708,8 +1779,10 @@
       <c r="C41" s="11" t="n">
         <v>56223300</v>
       </c>
-      <c r="D41" s="12" t="n">
-        <v>0.158</v>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.16%</t>
+        </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
@@ -1718,21 +1791,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-55391000</v>
-      </c>
-      <c r="J41" s="16" t="n">
-        <v>-0.155</v>
+        <v>-41442800</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>0.71%→0.59%</t>
+        </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>210→196</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -1748,8 +1823,10 @@
       <c r="C42" s="11" t="n">
         <v>73148100</v>
       </c>
-      <c r="D42" s="12" t="n">
-        <v>0.205</v>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>6.79%→7.00%</t>
+        </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
@@ -1758,21 +1835,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-41442800</v>
-      </c>
-      <c r="J42" s="16" t="n">
-        <v>-0.116</v>
+        <v>-55391000</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>2.40%→2.24%</t>
+        </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>210→196</t>
         </is>
       </c>
     </row>
@@ -1788,8 +1867,10 @@
       <c r="C43" s="11" t="n">
         <v>173553000</v>
       </c>
-      <c r="D43" s="12" t="n">
-        <v>0.487</v>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2.01%→2.51%</t>
+        </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
@@ -1807,8 +1888,10 @@
       <c r="I43" s="15" t="n">
         <v>-113848800</v>
       </c>
-      <c r="J43" s="16" t="n">
-        <v>-0.32</v>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>2.48%→2.15%</t>
+        </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
@@ -1828,8 +1911,10 @@
       <c r="C44" s="11" t="n">
         <v>54218400</v>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>0.152</v>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>0.56%→0.72%</t>
+        </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
@@ -1847,8 +1932,10 @@
       <c r="I44" s="15" t="n">
         <v>-39442000</v>
       </c>
-      <c r="J44" s="16" t="n">
-        <v>-0.111</v>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.24%</t>
+        </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
@@ -1868,8 +1955,10 @@
       <c r="C45" s="11" t="n">
         <v>19167500</v>
       </c>
-      <c r="D45" s="12" t="n">
-        <v>0.054</v>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>0.39%→0.44%</t>
+        </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1878,82 +1967,90 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-57195000</v>
-      </c>
-      <c r="J45" s="16" t="n">
-        <v>-0.161</v>
+        <v>-93873600</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>3.50%→3.22%</t>
+        </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>140→131</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>131528000</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>0.369</v>
+        <v>63632000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>2.61%→2.79%</t>
+        </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>65→75</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-93873600</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <v>-0.264</v>
+        <v>-57195000</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>2.57%→2.41%</t>
+        </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>140→131</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>63632000</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>0.179</v>
+        <v>131528000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2.47%→2.85%</t>
+        </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>65→75</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -1967,8 +2064,10 @@
       <c r="I47" s="15" t="n">
         <v>-178432000</v>
       </c>
-      <c r="J47" s="16" t="n">
-        <v>-0.501</v>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2.06%→1.55%</t>
+        </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -1988,8 +2087,10 @@
       <c r="C48" s="11" t="n">
         <v>112692600</v>
       </c>
-      <c r="D48" s="12" t="n">
-        <v>0.316</v>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>1.41%→1.74%</t>
+        </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -2007,8 +2108,10 @@
       <c r="I48" s="15" t="n">
         <v>-38868000</v>
       </c>
-      <c r="J48" s="16" t="n">
-        <v>-0.109</v>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>2.16%→2.05%</t>
+        </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -2028,8 +2131,10 @@
       <c r="C49" s="11" t="n">
         <v>112044800</v>
       </c>
-      <c r="D49" s="12" t="n">
-        <v>0.315</v>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2.43%→2.75%</t>
+        </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -2054,8 +2159,10 @@
       <c r="C50" s="11" t="n">
         <v>40344000</v>
       </c>
-      <c r="D50" s="12" t="n">
-        <v>0.113</v>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>0.89%→1.01%</t>
+        </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2080,8 +2187,10 @@
       <c r="C51" s="11" t="n">
         <v>42115200</v>
       </c>
-      <c r="D51" s="12" t="n">
-        <v>0.118</v>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>1.48%→1.60%</t>
+        </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -2106,8 +2215,10 @@
       <c r="C52" s="11" t="n">
         <v>20151500</v>
       </c>
-      <c r="D52" s="12" t="n">
-        <v>0.057</v>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>1.19%→1.25%</t>
+        </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -2132,8 +2243,10 @@
       <c r="C53" s="11" t="n">
         <v>103156000</v>
       </c>
-      <c r="D53" s="12" t="n">
-        <v>0.29</v>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>1.64%→1.94%</t>
+        </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
@@ -2158,8 +2271,10 @@
       <c r="C54" s="11" t="n">
         <v>58794000</v>
       </c>
-      <c r="D54" s="12" t="n">
-        <v>0.165</v>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>2.49%→2.66%</t>
+        </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
@@ -2227,7 +2342,7 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -2252,7 +2367,7 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -2273,8 +2388,10 @@
       <c r="C59" s="11" t="n">
         <v>878273550</v>
       </c>
-      <c r="D59" s="12" t="n">
-        <v>1.475</v>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.49%</t>
+        </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -2292,8 +2409,10 @@
       <c r="I59" s="15" t="n">
         <v>-914598300</v>
       </c>
-      <c r="J59" s="16" t="n">
-        <v>-1.536</v>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>1.31%→0.00%</t>
+        </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
@@ -2313,8 +2432,10 @@
       <c r="C60" s="11" t="n">
         <v>156412410</v>
       </c>
-      <c r="D60" s="12" t="n">
-        <v>0.263</v>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>1.82%→2.09%</t>
+        </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
@@ -2332,8 +2453,10 @@
       <c r="I60" s="15" t="n">
         <v>-1959930000</v>
       </c>
-      <c r="J60" s="16" t="n">
-        <v>-3.291</v>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>13.18%→9.24%</t>
+        </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
@@ -2353,8 +2476,10 @@
       <c r="C61" s="11" t="n">
         <v>732623500</v>
       </c>
-      <c r="D61" s="12" t="n">
-        <v>1.23</v>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>4.65%→6.62%</t>
+        </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
@@ -2372,8 +2497,10 @@
       <c r="I61" s="15" t="n">
         <v>-547495200</v>
       </c>
-      <c r="J61" s="16" t="n">
-        <v>-0.919</v>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>10.98%→9.23%</t>
+        </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
@@ -2393,8 +2520,10 @@
       <c r="C62" s="11" t="n">
         <v>805392000</v>
       </c>
-      <c r="D62" s="12" t="n">
-        <v>1.352</v>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>4.31%→6.39%</t>
+        </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
@@ -2412,8 +2541,10 @@
       <c r="I62" s="15" t="n">
         <v>-512057000</v>
       </c>
-      <c r="J62" s="16" t="n">
-        <v>-0.86</v>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>9.99%→9.59%</t>
+        </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
@@ -2433,8 +2564,10 @@
       <c r="C63" s="11" t="n">
         <v>523124000</v>
       </c>
-      <c r="D63" s="12" t="n">
-        <v>0.878</v>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>1.91%→2.91%</t>
+        </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
@@ -2459,8 +2592,10 @@
       <c r="C64" s="11" t="n">
         <v>42935200</v>
       </c>
-      <c r="D64" s="12" t="n">
-        <v>0.07199999999999999</v>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>7.44%→7.50%</t>
+        </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260707.xlsx
+++ b/reports/pdf_rolling5_20260707.xlsx
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>에코프로비엠  (편출)</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-5429902500</v>
+        <v>-3753486000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.96%→0.00%</t>
+          <t>1.63%→0.93%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>33→0</t>
+          <t>74→41</t>
         </is>
       </c>
     </row>
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에코프로비엠  (편출)</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-3753486000</v>
+        <v>-5429902500</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.63%→0.93%</t>
+          <t>0.96%→0.00%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>74→41</t>
+          <t>33→0</t>
         </is>
       </c>
     </row>
@@ -1791,23 +1791,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-41442800</v>
+        <v>-55391000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.59%</t>
+          <t>2.40%→2.24%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>210→196</t>
         </is>
       </c>
     </row>
@@ -1835,23 +1835,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-55391000</v>
+        <v>-41442800</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.24%</t>
+          <t>0.71%→0.59%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>210→196</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -2150,23 +2150,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>40344000</v>
+        <v>42115200</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.01%</t>
+          <t>1.48%→1.60%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G50" s="17" t="n"/>
@@ -2178,23 +2178,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>42115200</v>
+        <v>40344000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>1.48%→1.60%</t>
+          <t>0.89%→1.01%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G51" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260707.xlsx
+++ b/reports/pdf_rolling5_20260707.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>33</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1370655000</v>
+        <v>3138448500</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>1.40%→1.53%</t>
+          <t>2.02%→2.74%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>151→184</t>
+          <t>111→144</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>33</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3138448500</v>
+        <v>1370655000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2.02%→2.74%</t>
+          <t>1.40%→1.53%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>111→144</t>
+          <t>151→184</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1601,11 +1601,11 @@
         <v>91</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>24214190</v>
+        <v>24363430</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.39%→0.46%</t>
+          <t>0.38%→0.44%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1622,11 +1622,11 @@
         <v>-268</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-149656560</v>
+        <v>-148997280</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.30%</t>
+          <t>0.69%→0.28%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1645,11 +1645,11 @@
         <v>80</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>61204800</v>
+        <v>65468800</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>6.50%→6.67%</t>
+          <t>6.61%→6.78%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -1666,11 +1666,11 @@
         <v>-111</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-222999000</v>
+        <v>-226639800</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>3.76%→3.11%</t>
+          <t>3.63%→3.00%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -1689,11 +1689,11 @@
         <v>27</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>42375960</v>
+        <v>42752340</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>0.26%→0.39%</t>
+          <t>0.25%→0.37%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1703,23 +1703,23 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>다우데이타</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-63</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-178485300</v>
+        <v>-96500880</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>6.52%→6.00%</t>
+          <t>0.45%→0.18%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>796→733</t>
+          <t>107→44</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         <v>23</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>92508300</v>
+        <v>95431600</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.82%</t>
+          <t>1.53%→1.79%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>다우데이타</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-63</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-98463960</v>
+        <v>-187267500</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.20%</t>
+          <t>6.50%→5.98%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>107→44</t>
+          <t>796→733</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         <v>21</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>56223300</v>
+        <v>58289700</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1791,23 +1791,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-55391000</v>
+        <v>-42016800</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.24%</t>
+          <t>0.68%→0.57%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>210→196</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -1821,11 +1821,11 @@
         <v>19</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>73148100</v>
+        <v>79302200</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>6.79%→7.00%</t>
+          <t>7.00%→7.20%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1835,23 +1835,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-41442800</v>
+        <v>-59466400</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.59%</t>
+          <t>2.45%→2.28%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>210→196</t>
         </is>
       </c>
     </row>
@@ -1865,11 +1865,11 @@
         <v>17</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>173553000</v>
+        <v>185541400</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.51%</t>
+          <t>2.04%→2.54%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1886,11 +1886,11 @@
         <v>-13</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-113848800</v>
+        <v>-114595000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2.48%→2.15%</t>
+          <t>2.37%→2.06%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1909,11 +1909,11 @@
         <v>12</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>54218400</v>
+        <v>56776800</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>0.56%→0.72%</t>
+          <t>0.56%→0.71%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1930,11 +1930,11 @@
         <v>-13</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-39442000</v>
+        <v>-37256700</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.24%</t>
+          <t>0.31%→0.21%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1953,11 +1953,11 @@
         <v>11</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>19167500</v>
+        <v>19934200</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>0.39%→0.44%</t>
+          <t>0.38%→0.44%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1967,90 +1967,90 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-93873600</v>
+        <v>-62287200</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>3.50%→3.22%</t>
+          <t>2.66%→2.49%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>140→131</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>63632000</v>
+        <v>145386000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.79%</t>
+          <t>2.60%→2.99%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>65→75</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-57195000</v>
+        <v>-106198200</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.41%</t>
+          <t>3.76%→3.46%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>140→131</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>131528000</v>
+        <v>64534000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.47%→2.85%</t>
+          <t>2.52%→2.69%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>65→75</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2062,11 +2062,11 @@
         <v>-8</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-178432000</v>
+        <v>-170560000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2.06%→1.55%</t>
+          <t>1.87%→1.40%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2085,11 +2085,11 @@
         <v>9</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>112692600</v>
+        <v>123246000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.74%</t>
+          <t>1.47%→1.80%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2106,11 +2106,11 @@
         <v>-4</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-38868000</v>
+        <v>-42344800</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>2.16%→2.05%</t>
+          <t>2.24%→2.12%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2129,11 +2129,11 @@
         <v>8</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>112044800</v>
+        <v>119588800</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.43%→2.75%</t>
+          <t>2.46%→2.79%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2157,11 +2157,11 @@
         <v>6</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>42115200</v>
+        <v>43788000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>1.48%→1.60%</t>
+          <t>1.46%→1.58%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2185,11 +2185,11 @@
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>40344000</v>
+        <v>41475600</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.01%</t>
+          <t>0.87%→0.99%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2213,11 +2213,11 @@
         <v>5</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>20151500</v>
+        <v>22181000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.19%→1.25%</t>
+          <t>1.24%→1.30%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2241,11 +2241,11 @@
         <v>4</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>103156000</v>
+        <v>105780000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.64%→1.94%</t>
+          <t>1.60%→1.89%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2269,11 +2269,11 @@
         <v>3</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>58794000</v>
+        <v>60270000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.49%→2.66%</t>
+          <t>2.43%→2.59%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
